--- a/Daily_Report/Top 7 broker List with its Turnover 2024-08-06.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-08-06.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="269">
   <si>
     <t>Date: 2024-08-06</t>
   </si>
@@ -68,16 +68,16 @@
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
-    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
-    <t>Oxford Securities Pvt.Ltd</t>
+    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
     <t>58</t>
@@ -89,79 +89,79 @@
     <t>34</t>
   </si>
   <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>57</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>2,848,874,256.4</t>
-  </si>
-  <si>
-    <t>2,150,860,558.01</t>
-  </si>
-  <si>
-    <t>2,132,251,428.21</t>
-  </si>
-  <si>
-    <t>2,003,721,625.2</t>
-  </si>
-  <si>
-    <t>1,580,807,673.3</t>
-  </si>
-  <si>
-    <t>1,551,339,476.6</t>
-  </si>
-  <si>
-    <t>1,378,373,605.46</t>
-  </si>
-  <si>
-    <t>1,365,853,349.0</t>
-  </si>
-  <si>
-    <t>1,374,482,458.81</t>
-  </si>
-  <si>
-    <t>886,813,004.3</t>
-  </si>
-  <si>
-    <t>1,025,870,124.2</t>
-  </si>
-  <si>
-    <t>778,466,994.9</t>
-  </si>
-  <si>
-    <t>627,400,895.5</t>
-  </si>
-  <si>
-    <t>150,579,329.36</t>
-  </si>
-  <si>
-    <t>1,483,020,907.4</t>
-  </si>
-  <si>
-    <t>776,378,099.2</t>
-  </si>
-  <si>
-    <t>1,245,438,423.91</t>
-  </si>
-  <si>
-    <t>977,851,501.0</t>
-  </si>
-  <si>
-    <t>802,340,678.4</t>
-  </si>
-  <si>
-    <t>923,938,581.1</t>
-  </si>
-  <si>
-    <t>1,227,794,276.09</t>
+    <t>38</t>
+  </si>
+  <si>
+    <t>2,796,832,278.3</t>
+  </si>
+  <si>
+    <t>2,101,202,319.8</t>
+  </si>
+  <si>
+    <t>2,066,452,136.11</t>
+  </si>
+  <si>
+    <t>1,881,768,083.83</t>
+  </si>
+  <si>
+    <t>1,798,190,106.7</t>
+  </si>
+  <si>
+    <t>1,746,746,307.4</t>
+  </si>
+  <si>
+    <t>1,364,323,473.55</t>
+  </si>
+  <si>
+    <t>1,433,056,808.2</t>
+  </si>
+  <si>
+    <t>1,165,956,332.96</t>
+  </si>
+  <si>
+    <t>949,043,914.2</t>
+  </si>
+  <si>
+    <t>967,831,073.65</t>
+  </si>
+  <si>
+    <t>874,702,150.0</t>
+  </si>
+  <si>
+    <t>857,229,061.2</t>
+  </si>
+  <si>
+    <t>688,809,194.7</t>
+  </si>
+  <si>
+    <t>1,363,775,470.09</t>
+  </si>
+  <si>
+    <t>935,245,986.84</t>
+  </si>
+  <si>
+    <t>1,117,408,221.91</t>
+  </si>
+  <si>
+    <t>913,937,010.18</t>
+  </si>
+  <si>
+    <t>923,487,956.7</t>
+  </si>
+  <si>
+    <t>889,517,246.2</t>
+  </si>
+  <si>
+    <t>675,514,278.85</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,349 +179,310 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>JOSHI</t>
-  </si>
-  <si>
-    <t>199,971,832.6</t>
-  </si>
-  <si>
-    <t>ADBL</t>
-  </si>
-  <si>
-    <t>88,777,730.1</t>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>92,672,481.5</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>88,641,155.5</t>
+    <t>92,497,915.5</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>80,736,361.5</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>68,244,641.4</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>66,054,919.9</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>204,431,386.2</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>62,854,635.6</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>38,103,216.1</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>36,410,484.6</t>
+  </si>
+  <si>
+    <t>35,690,110.6</t>
+  </si>
+  <si>
+    <t>41,644,740.6</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>40,836,623.7</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>21,886,541.4</t>
+  </si>
+  <si>
+    <t>19,991,730.7</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>19,758,288.5</t>
+  </si>
+  <si>
+    <t>57,355,775.1</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>26,374,023.3</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>22,712,935.3</t>
+  </si>
+  <si>
+    <t>22,577,270.4</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>22,495,838.0</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>47,459,414.4</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>40,520,795.1</t>
   </si>
   <si>
     <t>NABIL</t>
   </si>
   <si>
-    <t>76,312,354.2</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>65,463,178.9</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>294,847,038.5</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>185,500,583.4</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>133,048,458.9</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>74,656,496.3</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>71,081,732.0</t>
-  </si>
-  <si>
-    <t>142,269,749.5</t>
-  </si>
-  <si>
-    <t>83,204,371.0</t>
-  </si>
-  <si>
-    <t>66,376,176.0</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>56,760,516.6</t>
-  </si>
-  <si>
-    <t>41,520,402.1</t>
-  </si>
-  <si>
-    <t>226,975,178.9</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>107,217,969.5</t>
-  </si>
-  <si>
-    <t>52,663,550.0</t>
-  </si>
-  <si>
-    <t>SMATA</t>
-  </si>
-  <si>
-    <t>44,665,951.2</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>38,514,079.1</t>
-  </si>
-  <si>
-    <t>NLICL</t>
-  </si>
-  <si>
-    <t>112,374,942.0</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>85,698,388.0</t>
-  </si>
-  <si>
-    <t>62,318,680.5</t>
-  </si>
-  <si>
-    <t>58,207,170.9</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>36,730,135.4</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>44,660,244.4</t>
-  </si>
-  <si>
-    <t>43,341,885.3</t>
-  </si>
-  <si>
-    <t>SKBBL</t>
-  </si>
-  <si>
-    <t>40,433,382.29</t>
-  </si>
-  <si>
-    <t>37,476,234.2</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>26,336,771.2</t>
-  </si>
-  <si>
-    <t>USHL</t>
-  </si>
-  <si>
-    <t>11,886,640.0</t>
-  </si>
-  <si>
-    <t>4,579,085.8</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>4,349,369.0</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>4,071,247.0</t>
-  </si>
-  <si>
-    <t>3,882,666.3</t>
+    <t>40,176,598.2</t>
+  </si>
+  <si>
+    <t>37,565,578.0</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>31,972,925.9</t>
+  </si>
+  <si>
+    <t>55,758,486.4</t>
+  </si>
+  <si>
+    <t>41,707,258.0</t>
+  </si>
+  <si>
+    <t>17,277,165.5</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>16,675,788.4</t>
+  </si>
+  <si>
+    <t>16,591,537.3</t>
+  </si>
+  <si>
+    <t>34,000,556.79</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>24,142,487.3</t>
+  </si>
+  <si>
+    <t>14,114,166.1</t>
+  </si>
+  <si>
+    <t>12,979,021.5</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>12,597,236.0</t>
   </si>
   <si>
     <t>Sell Amount</t>
   </si>
   <si>
-    <t>222,547,671.9</t>
-  </si>
-  <si>
-    <t>134,919,903.1</t>
-  </si>
-  <si>
-    <t>BHDC</t>
-  </si>
-  <si>
-    <t>94,498,510.8</t>
-  </si>
-  <si>
-    <t>MEL</t>
-  </si>
-  <si>
-    <t>93,404,466.8</t>
+    <t>87,930,528.7</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>59,591,339.9</t>
   </si>
   <si>
     <t>IGI</t>
   </si>
   <si>
-    <t>74,582,426.3</t>
-  </si>
-  <si>
-    <t>69,343,773.1</t>
-  </si>
-  <si>
-    <t>TPC</t>
-  </si>
-  <si>
-    <t>54,315,505.0</t>
-  </si>
-  <si>
-    <t>51,504,738.3</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>28,759,461.0</t>
-  </si>
-  <si>
-    <t>MMF1</t>
-  </si>
-  <si>
-    <t>24,539,556.7</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>186,306,924.8</t>
-  </si>
-  <si>
-    <t>128,489,974.4</t>
-  </si>
-  <si>
-    <t>126,307,131.9</t>
+    <t>48,303,357.0</t>
+  </si>
+  <si>
+    <t>38,250,958.9</t>
+  </si>
+  <si>
+    <t>33,380,949.0</t>
+  </si>
+  <si>
+    <t>63,398,337.8</t>
+  </si>
+  <si>
+    <t>31,541,579.4</t>
+  </si>
+  <si>
+    <t>25,876,390.1</t>
+  </si>
+  <si>
+    <t>17,955,731.5</t>
+  </si>
+  <si>
+    <t>17,346,301.0</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>72,052,725.09</t>
+  </si>
+  <si>
+    <t>38,051,302.4</t>
+  </si>
+  <si>
+    <t>37,176,474.7</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>34,295,451.4</t>
+  </si>
+  <si>
+    <t>29,627,839.0</t>
+  </si>
+  <si>
+    <t>PCBL</t>
+  </si>
+  <si>
+    <t>37,004,146.7</t>
+  </si>
+  <si>
+    <t>34,557,966.7</t>
+  </si>
+  <si>
+    <t>30,132,419.4</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>28,518,068.5</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>26,004,850.6</t>
+  </si>
+  <si>
+    <t>37,071,767.6</t>
+  </si>
+  <si>
+    <t>29,683,401.1</t>
+  </si>
+  <si>
+    <t>23,836,266.1</t>
+  </si>
+  <si>
+    <t>17,739,471.0</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>16,959,175.1</t>
+  </si>
+  <si>
+    <t>73,036,839.8</t>
+  </si>
+  <si>
+    <t>34,643,405.29</t>
+  </si>
+  <si>
+    <t>17,885,107.89</t>
+  </si>
+  <si>
+    <t>16,852,293.39</t>
+  </si>
+  <si>
+    <t>14,323,893.4</t>
+  </si>
+  <si>
+    <t>25,686,630.7</t>
+  </si>
+  <si>
+    <t>22,310,773.1</t>
+  </si>
+  <si>
+    <t>16,089,933.6</t>
   </si>
   <si>
     <t>CITY</t>
   </si>
   <si>
-    <t>51,680,577.0</t>
-  </si>
-  <si>
-    <t>SMH</t>
-  </si>
-  <si>
-    <t>41,270,673.0</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>252,203,370.5</t>
-  </si>
-  <si>
-    <t>117,943,039.3</t>
-  </si>
-  <si>
-    <t>58,936,582.9</t>
-  </si>
-  <si>
-    <t>GUFL</t>
-  </si>
-  <si>
-    <t>26,420,144.8</t>
-  </si>
-  <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>20,199,553.39</t>
-  </si>
-  <si>
-    <t>477,575,817.0</t>
-  </si>
-  <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>43,824,659.5</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>27,784,631.0</t>
-  </si>
-  <si>
-    <t>21,229,101.89</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>13,737,209.3</t>
-  </si>
-  <si>
-    <t>SPL</t>
-  </si>
-  <si>
-    <t>97,354,634.0</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>70,766,752.5</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>60,201,060.5</t>
-  </si>
-  <si>
-    <t>RBCL</t>
-  </si>
-  <si>
-    <t>41,941,993.0</t>
-  </si>
-  <si>
-    <t>24,972,903.3</t>
-  </si>
-  <si>
-    <t>776,375,701.7</t>
-  </si>
-  <si>
-    <t>163,906,170.4</t>
-  </si>
-  <si>
-    <t>GCIL</t>
-  </si>
-  <si>
-    <t>67,754,480.9</t>
-  </si>
-  <si>
-    <t>26,060,770.4</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>9,634,313.19</t>
+    <t>15,254,904.5</t>
+  </si>
+  <si>
+    <t>14,350,173.6</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -539,109 +500,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>1,178,673,360.8</t>
-  </si>
-  <si>
-    <t>905,414,997.4</t>
-  </si>
-  <si>
-    <t>878,859,565.0</t>
-  </si>
-  <si>
-    <t>677,835,152.2</t>
-  </si>
-  <si>
-    <t>544,021,081.9</t>
+    <t>1,397,880,383.4</t>
+  </si>
+  <si>
+    <t>483,633,519.7</t>
+  </si>
+  <si>
+    <t>431,830,592.2</t>
+  </si>
+  <si>
+    <t>422,373,193.9</t>
+  </si>
+  <si>
+    <t>410,367,577.8</t>
+  </si>
+  <si>
+    <t>Promoter Shares/debenture</t>
+  </si>
+  <si>
+    <t>6,435,208,721.97</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>5,686,070,665.4</t>
-  </si>
-  <si>
-    <t>Promoter Shares/debenture</t>
-  </si>
-  <si>
-    <t>5,197,811,575.67</t>
+    <t>5,580,116,464.5</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>2,177,119,263.9</t>
+    <t>2,100,071,667.8</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,959,080,149.0</t>
+    <t>2,050,154,578.1</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>1,584,175,979.7</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>1,289,958,410.2</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>1,210,286,516.9</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>801,678,416.1</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>789,592,350.4</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>629,452,266.5</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>623,894,684.2</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>1,292,188,949.09</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>1,198,807,939.0</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>1,038,029,649.5</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>975,128,917.3</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>951,276,384.8</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>903,538,752.5</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>893,440,983.2</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>460,475,820.1</t>
+    <t>508,871,850.9</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>78,012,301.9</t>
+    <t>65,888,163.1</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>52,929,883.02</t>
+    <t>40,762,322.72</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>3,920,529.0</t>
+    <t>6,604,481.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -653,214 +614,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>542,409,530.7</t>
-  </si>
-  <si>
-    <t>203,964,516.1</t>
-  </si>
-  <si>
-    <t>202,184,537.3</t>
-  </si>
-  <si>
-    <t>109,208,717.6</t>
-  </si>
-  <si>
-    <t>63,800,818.5</t>
-  </si>
-  <si>
-    <t>300,552,875.7</t>
-  </si>
-  <si>
-    <t>262,490,087.4</t>
-  </si>
-  <si>
-    <t>261,191,782.9</t>
-  </si>
-  <si>
-    <t>231,553,000.5</t>
-  </si>
-  <si>
-    <t>100,766,278.3</t>
-  </si>
-  <si>
-    <t>192,549,973.4</t>
-  </si>
-  <si>
-    <t>147,510,298.5</t>
-  </si>
-  <si>
-    <t>130,530,368.0</t>
-  </si>
-  <si>
-    <t>123,476,113.3</t>
-  </si>
-  <si>
-    <t>79,366,135.59</t>
-  </si>
-  <si>
-    <t>292,175,700.1</t>
-  </si>
-  <si>
-    <t>239,882,089.2</t>
-  </si>
-  <si>
-    <t>157,595,099.4</t>
-  </si>
-  <si>
-    <t>89,285,375.3</t>
-  </si>
-  <si>
-    <t>60,982,307.6</t>
-  </si>
-  <si>
-    <t>222,142,308.2</t>
-  </si>
-  <si>
-    <t>175,466,814.6</t>
-  </si>
-  <si>
-    <t>103,605,760.4</t>
-  </si>
-  <si>
-    <t>65,261,590.2</t>
-  </si>
-  <si>
-    <t>52,021,814.4</t>
-  </si>
-  <si>
-    <t>166,487,955.1</t>
-  </si>
-  <si>
-    <t>102,005,483.7</t>
-  </si>
-  <si>
-    <t>99,935,039.5</t>
-  </si>
-  <si>
-    <t>96,672,490.2</t>
-  </si>
-  <si>
-    <t>42,137,610.2</t>
-  </si>
-  <si>
-    <t>48,543,200.8</t>
-  </si>
-  <si>
-    <t>36,013,367.5</t>
-  </si>
-  <si>
-    <t>14,257,285.8</t>
-  </si>
-  <si>
-    <t>14,221,272.1</t>
-  </si>
-  <si>
-    <t>8,241,351.3</t>
-  </si>
-  <si>
-    <t>617,531,483.6</t>
-  </si>
-  <si>
-    <t>280,923,247.89</t>
-  </si>
-  <si>
-    <t>131,453,329.4</t>
-  </si>
-  <si>
-    <t>78,268,721.2</t>
-  </si>
-  <si>
-    <t>75,750,305.4</t>
-  </si>
-  <si>
-    <t>207,113,699.8</t>
-  </si>
-  <si>
-    <t>176,835,711.4</t>
-  </si>
-  <si>
-    <t>115,841,167.4</t>
-  </si>
-  <si>
-    <t>57,655,497.0</t>
-  </si>
-  <si>
-    <t>38,781,783.7</t>
-  </si>
-  <si>
-    <t>406,819,941.5</t>
-  </si>
-  <si>
-    <t>380,645,259.7</t>
-  </si>
-  <si>
-    <t>151,271,186.4</t>
-  </si>
-  <si>
-    <t>65,457,527.5</t>
-  </si>
-  <si>
-    <t>53,997,367.4</t>
-  </si>
-  <si>
-    <t>282,810,694.3</t>
-  </si>
-  <si>
-    <t>262,014,453.6</t>
-  </si>
-  <si>
-    <t>122,366,548.6</t>
-  </si>
-  <si>
-    <t>76,848,643.0</t>
-  </si>
-  <si>
-    <t>54,991,367.1</t>
-  </si>
-  <si>
-    <t>537,956,318.9</t>
-  </si>
-  <si>
-    <t>93,700,031.5</t>
-  </si>
-  <si>
-    <t>74,114,560.0</t>
-  </si>
-  <si>
-    <t>19,980,054.6</t>
-  </si>
-  <si>
-    <t>18,676,231.0</t>
-  </si>
-  <si>
-    <t>266,030,347.8</t>
-  </si>
-  <si>
-    <t>215,681,904.1</t>
-  </si>
-  <si>
-    <t>125,526,721.0</t>
-  </si>
-  <si>
-    <t>72,560,108.59</t>
-  </si>
-  <si>
-    <t>54,080,351.6</t>
-  </si>
-  <si>
-    <t>821,765,865.4</t>
-  </si>
-  <si>
-    <t>177,635,273.2</t>
-  </si>
-  <si>
-    <t>135,753,429.4</t>
-  </si>
-  <si>
-    <t>17,723,800.39</t>
-  </si>
-  <si>
-    <t>17,192,097.89</t>
+    <t>435,312,572.8</t>
+  </si>
+  <si>
+    <t>362,014,546.4</t>
+  </si>
+  <si>
+    <t>125,490,158.4</t>
+  </si>
+  <si>
+    <t>106,890,005.3</t>
+  </si>
+  <si>
+    <t>84,317,811.59</t>
+  </si>
+  <si>
+    <t>392,503,674.3</t>
+  </si>
+  <si>
+    <t>231,545,334.4</t>
+  </si>
+  <si>
+    <t>168,118,544.1</t>
+  </si>
+  <si>
+    <t>77,518,657.2</t>
+  </si>
+  <si>
+    <t>50,718,649.8</t>
+  </si>
+  <si>
+    <t>238,197,408.1</t>
+  </si>
+  <si>
+    <t>222,309,399.7</t>
+  </si>
+  <si>
+    <t>90,656,097.3</t>
+  </si>
+  <si>
+    <t>87,972,772.0</t>
+  </si>
+  <si>
+    <t>86,828,459.9</t>
+  </si>
+  <si>
+    <t>253,523,947.0</t>
+  </si>
+  <si>
+    <t>219,402,250.0</t>
+  </si>
+  <si>
+    <t>88,031,419.7</t>
+  </si>
+  <si>
+    <t>68,225,749.09</t>
+  </si>
+  <si>
+    <t>66,862,658.6</t>
+  </si>
+  <si>
+    <t>195,616,729.2</t>
+  </si>
+  <si>
+    <t>160,500,017.4</t>
+  </si>
+  <si>
+    <t>155,821,866.69</t>
+  </si>
+  <si>
+    <t>112,413,230.9</t>
+  </si>
+  <si>
+    <t>60,302,356.0</t>
+  </si>
+  <si>
+    <t>211,032,355.2</t>
+  </si>
+  <si>
+    <t>205,223,970.0</t>
+  </si>
+  <si>
+    <t>116,517,252.4</t>
+  </si>
+  <si>
+    <t>81,622,950.7</t>
+  </si>
+  <si>
+    <t>59,962,260.3</t>
+  </si>
+  <si>
+    <t>190,964,154.1</t>
+  </si>
+  <si>
+    <t>159,987,845.0</t>
+  </si>
+  <si>
+    <t>78,427,903.8</t>
+  </si>
+  <si>
+    <t>61,161,203.6</t>
+  </si>
+  <si>
+    <t>55,360,191.7</t>
+  </si>
+  <si>
+    <t>283,872,167.7</t>
+  </si>
+  <si>
+    <t>270,304,289.3</t>
+  </si>
+  <si>
+    <t>134,186,446.7</t>
+  </si>
+  <si>
+    <t>128,173,151.7</t>
+  </si>
+  <si>
+    <t>118,728,861.3</t>
+  </si>
+  <si>
+    <t>266,387,903.1</t>
+  </si>
+  <si>
+    <t>216,349,502.3</t>
+  </si>
+  <si>
+    <t>95,302,647.7</t>
+  </si>
+  <si>
+    <t>65,942,297.4</t>
+  </si>
+  <si>
+    <t>54,414,083.0</t>
+  </si>
+  <si>
+    <t>368,218,570.7</t>
+  </si>
+  <si>
+    <t>267,460,279.9</t>
+  </si>
+  <si>
+    <t>100,201,049.3</t>
+  </si>
+  <si>
+    <t>83,832,689.9</t>
+  </si>
+  <si>
+    <t>59,654,699.6</t>
+  </si>
+  <si>
+    <t>267,328,954.2</t>
+  </si>
+  <si>
+    <t>208,743,896.5</t>
+  </si>
+  <si>
+    <t>125,282,643.6</t>
+  </si>
+  <si>
+    <t>64,942,371.5</t>
+  </si>
+  <si>
+    <t>56,788,307.8</t>
+  </si>
+  <si>
+    <t>249,402,036.5</t>
+  </si>
+  <si>
+    <t>226,313,910.5</t>
+  </si>
+  <si>
+    <t>70,217,891.4</t>
+  </si>
+  <si>
+    <t>69,905,799.9</t>
+  </si>
+  <si>
+    <t>68,114,798.0</t>
+  </si>
+  <si>
+    <t>260,541,068.7</t>
+  </si>
+  <si>
+    <t>187,316,172.4</t>
+  </si>
+  <si>
+    <t>88,917,134.4</t>
+  </si>
+  <si>
+    <t>81,190,503.4</t>
+  </si>
+  <si>
+    <t>60,700,140.0</t>
+  </si>
+  <si>
+    <t>197,943,780.8</t>
+  </si>
+  <si>
+    <t>181,978,164.4</t>
+  </si>
+  <si>
+    <t>63,348,197.9</t>
+  </si>
+  <si>
+    <t>46,793,943.4</t>
+  </si>
+  <si>
+    <t>31,818,991.0</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1630,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.07019328148680588</v>
+        <v>0.03313480118883966</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1678,52 +1639,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1370832885479083</v>
+        <v>0.09729257590932913</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.06672278307227295</v>
+        <v>0.02015277289625217</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.11327680254853</v>
+        <v>0.03047972573924341</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P9" s="18">
-        <v>0.07108704233792891</v>
+        <v>0.02639287927520439</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S9" s="16">
-        <v>0.02878818277600969</v>
+        <v>0.03192134207685573</v>
       </c>
       <c r="T9" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="U9" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="U9" s="17" t="s">
-        <v>105</v>
-      </c>
       <c r="V9" s="18">
-        <v>0.008623670645545416</v>
+        <v>0.0249211843519263</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1735,7 +1696,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.03116238981083868</v>
+        <v>0.03307238557623593</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1744,52 +1705,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.08624482080401678</v>
+        <v>0.02991365229693004</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03902183855955912</v>
+        <v>0.01976170799526625</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M10" s="16">
-        <v>0.05350941375865927</v>
+        <v>0.01401555458753473</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P10" s="18">
-        <v>0.05421177379605019</v>
+        <v>0.02253421089851445</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02793836291395771</v>
+        <v>0.02387711244804661</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="U10" s="17" t="s">
         <v>106</v>
       </c>
       <c r="V10" s="18">
-        <v>0.003322093358332872</v>
+        <v>0.0176955742300473</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1801,7 +1762,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03111444996242552</v>
+        <v>0.02886707298339463</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1810,52 +1771,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06185824478696002</v>
+        <v>0.01813400629770235</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.01059136140515715</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.01206999709218785</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.0223427979334906</v>
+      </c>
+      <c r="Q11" s="15" t="s">
         <v>76</v>
-      </c>
-      <c r="J11" s="14">
-        <v>0.03112961966953495</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="M11" s="16">
-        <v>0.02628286750897517</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0.03942205086208067</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>99</v>
       </c>
       <c r="R11" s="15" t="s">
         <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02606352955615878</v>
+        <v>0.009891055974646224</v>
       </c>
       <c r="T11" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="U11" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="U11" s="17" t="s">
-        <v>108</v>
-      </c>
       <c r="V11" s="18">
-        <v>0.003155435494971263</v>
+        <v>0.0103451757399399</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1867,7 +1828,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02678684537534929</v>
+        <v>0.02440069142847607</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1876,52 +1837,52 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03471005873531523</v>
+        <v>0.01732840491222458</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02661999229971195</v>
+        <v>0.009674422335101117</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02229149530466424</v>
+        <v>0.01199790271394551</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03682115913474166</v>
+        <v>0.02089077114818496</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02415733936077934</v>
+        <v>0.009546771806159766</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V12" s="18">
-        <v>0.002953660011968465</v>
+        <v>0.009513155605413938</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1933,61 +1894,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02297861295665713</v>
+        <v>0.02361776228503419</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.03304804290323943</v>
+        <v>0.01698556596082433</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01947256385934556</v>
+        <v>0.009561454705258288</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01922127236419667</v>
+        <v>0.01195462830585041</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02323504371871143</v>
+        <v>0.01778061495326322</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="R13" s="15" t="s">
         <v>103</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01697679431050198</v>
+        <v>0.00949853864279593</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V13" s="18">
-        <v>0.002816846089202536</v>
+        <v>0.0092333205755243</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1998,7 +1959,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2007,7 +1968,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2016,7 +1977,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2025,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2034,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2043,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2052,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2064,130 +2025,130 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16" s="10">
-        <v>0.07811775876034063</v>
+        <v>0.03143932847966373</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G16" s="12">
-        <v>0.03224001334803295</v>
+        <v>0.03017240995909165</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J16" s="14">
-        <v>0.0873756829683085</v>
+        <v>0.03486784128261296</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1258674694768673</v>
+        <v>0.01966456282151663</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="O16" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.02061615591247653</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="R16" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="P16" s="18">
-        <v>0.302108741668138</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>154</v>
-      </c>
       <c r="S16" s="16">
-        <v>0.06275520959046806</v>
+        <v>0.04181307811591369</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="V16" s="18">
-        <v>0.5632549104427336</v>
+        <v>0.01882737576387425</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04735902358515903</v>
+        <v>0.02130672631403605</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G17" s="12">
-        <v>0.02525291786012074</v>
+        <v>0.01501120530030741</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J17" s="14">
-        <v>0.06026023605849608</v>
+        <v>0.01841383196594614</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="M17" s="16">
-        <v>0.05886198852010074</v>
+        <v>0.01836462579897916</v>
       </c>
       <c r="N17" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.01650737649451</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="O17" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.02772295468968356</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="S17" s="16">
-        <v>0.04561654851657373</v>
+        <v>0.01983310636080065</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1189127314617289</v>
+        <v>0.01635299365035981</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2199,428 +2160,428 @@
         <v>116</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03317047447345525</v>
+        <v>0.01727073781820062</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02394610757456669</v>
+        <v>0.01231503975422177</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05923650946081596</v>
+        <v>0.0179904842944889</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02941355833004861</v>
+        <v>0.01601282307789538</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01757622478008249</v>
+        <v>0.01325569861116843</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="S18" s="16">
-        <v>0.03880585868409661</v>
+        <v>0.01023909873129868</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04915538184394392</v>
+        <v>0.01179334220361512</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>118</v>
-      </c>
       <c r="D19" s="10">
-        <v>0.03278644769602124</v>
+        <v>0.01367652940677948</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01337114156140767</v>
+        <v>0.008545455775866975</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02423756237949163</v>
+        <v>0.01659629603836825</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="L19" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.01515493261101369</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="O19" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.01318553658738044</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>150</v>
-      </c>
       <c r="P19" s="18">
-        <v>0.01342927559029581</v>
+        <v>0.009865181069511664</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02703598640571073</v>
+        <v>0.009647819679713151</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01890689889647359</v>
+        <v>0.01118129592852815</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D20" s="10">
-        <v>0.026179613274419</v>
+        <v>0.0119352702194534</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01140918066892457</v>
+        <v>0.008255416832802223</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01935544394717383</v>
+        <v>0.01433753943886309</v>
       </c>
       <c r="K20" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.01381937063523355</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="O20" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.01008101781502897</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>152</v>
-      </c>
       <c r="P20" s="18">
-        <v>0.008689994065706311</v>
+        <v>0.009431247028226128</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01609763928313871</v>
+        <v>0.008200328427383856</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="V20" s="18">
-        <v>0.006989623975558333</v>
+        <v>0.01051816074281895</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2397494853771059</v>
+        <v>0.2713364061362816</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2191623572209653</v>
+        <v>0.2352819951480639</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D33" s="22">
-        <v>0.09179682312089064</v>
+        <v>0.08854816115351098</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D34" s="22">
-        <v>0.08260334511727577</v>
+        <v>0.08644343940956201</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05448430977860783</v>
+        <v>0.06679575373394157</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05054695999298142</v>
+        <v>0.05439026055114348</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04376784759080998</v>
+        <v>0.0510309467927115</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="D38" s="22">
-        <v>0.04111567897346264</v>
+        <v>0.03380225097578655</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D39" s="22">
-        <v>0.04010995239559687</v>
+        <v>0.03329264984658478</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="D40" s="22">
-        <v>0.03809712606076247</v>
+        <v>0.02654044697001876</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D41" s="22">
-        <v>0.03767136016097103</v>
+        <v>0.02630611511331606</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01941566459406807</v>
+        <v>0.02145625187505261</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D43" s="22">
-        <v>0.003289338162365714</v>
+        <v>0.002778131705571508</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D44" s="22">
-        <v>0.002231754222179143</v>
+        <v>0.001718716926393584</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0001653065650196061</v>
+        <v>0.0002784736620612302</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2999,331 +2960,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1903943389152667</v>
+        <v>0.1556448615733927</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1397361045004586</v>
+        <v>0.186799562612971</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="J9" s="14">
-        <v>0.09030359687067648</v>
+        <v>0.1152687758587022</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1458165128456088</v>
+        <v>0.1347264570902902</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1405245634570263</v>
+        <v>0.1087853439250601</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1073188413053757</v>
+        <v>0.120814542046531</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="V9" s="18">
-        <v>0.03521773821532213</v>
+        <v>0.1399698515800707</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="D10" s="10">
-        <v>0.07159477665319676</v>
+        <v>0.1294373456745298</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1220395652439964</v>
+        <v>0.1101965918360681</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="J10" s="14">
-        <v>0.06918053684871167</v>
+        <v>0.10758023174855</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1197182713322547</v>
+        <v>0.1165936716034881</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1109982052615584</v>
+        <v>0.0892564233347642</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="S10" s="16">
-        <v>0.06575316701381233</v>
+        <v>0.1174892822904959</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02612743552063403</v>
+        <v>0.1172653319404584</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D11" s="10">
-        <v>0.07096997589338741</v>
+        <v>0.04486867495546667</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="G11" s="12">
-        <v>0.1214359442909016</v>
+        <v>0.08001064082015773</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06121715585369719</v>
+        <v>0.04387040750464991</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="M11" s="16">
-        <v>0.07865119456614626</v>
+        <v>0.04678122689849639</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="P11" s="18">
-        <v>0.065539763090673</v>
+        <v>0.08665483483610135</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="S11" s="16">
-        <v>0.06441854990954209</v>
+        <v>0.06670530912610532</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01034355688727946</v>
+        <v>0.05748483062886021</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03833399012071609</v>
+        <v>0.03821823930213327</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="G12" s="12">
-        <v>0.1076559796671502</v>
+        <v>0.03689252408943585</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="J12" s="14">
-        <v>0.05790879615151987</v>
+        <v>0.04257188950217092</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04455977026803214</v>
+        <v>0.03625619420706656</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="P12" s="18">
-        <v>0.04128370028958918</v>
+        <v>0.06251465319553913</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="S12" s="16">
-        <v>0.06231549680658723</v>
+        <v>0.04672856633742897</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="V12" s="18">
-        <v>0.0103174292105325</v>
+        <v>0.0448289608628203</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02239509811872931</v>
+        <v>0.03014761101486247</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04684928454554491</v>
+        <v>0.02413791823950945</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0372217528148765</v>
+        <v>0.04201813261615173</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03043452086010855</v>
+        <v>0.03553182731418906</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03290837669797134</v>
+        <v>0.03353502823495431</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02716208208170599</v>
+        <v>0.03432797312693491</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="V13" s="18">
-        <v>0.005979040274243818</v>
+        <v>0.04057702793601545</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3334,7 +3295,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3343,7 +3304,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3352,7 +3313,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3361,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3370,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3379,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3388,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3397,331 +3358,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2167633345742497</v>
+        <v>0.1014977443955081</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="G16" s="12">
-        <v>0.09629341103898613</v>
+        <v>0.126778797353201</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1907936072255421</v>
+        <v>0.1781887730500036</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1411427070223747</v>
+        <v>0.1420626465594528</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="P16" s="18">
-        <v>0.3403047239623998</v>
+        <v>0.1386961454023887</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1714842894239026</v>
+        <v>0.149157933007347</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="V16" s="18">
-        <v>0.5961851432331765</v>
+        <v>0.145085666733378</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D17" s="10">
-        <v>0.09860851080699877</v>
+        <v>0.09664658528050855</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08221626025055308</v>
+        <v>0.1029646218554494</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1785179996430098</v>
+        <v>0.1294296999317301</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1307638996878357</v>
+        <v>0.1109296614677083</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="P17" s="18">
-        <v>0.05927351763443645</v>
+        <v>0.1258564985185723</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1390294692768988</v>
+        <v>0.1072371938652137</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1288730954338888</v>
+        <v>0.1333834445628123</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="D18" s="10">
-        <v>0.04614220129396372</v>
+        <v>0.04797800988680044</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05385805554367389</v>
+        <v>0.04535624523252537</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="J18" s="14">
-        <v>0.07094434755613713</v>
+        <v>0.04848941214221579</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="M18" s="16">
-        <v>0.06106963515342909</v>
+        <v>0.06657709027831407</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="P18" s="18">
-        <v>0.04688398294859163</v>
+        <v>0.03904920349543151</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="S18" s="16">
-        <v>0.08091505624230694</v>
+        <v>0.05090443530540593</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="V18" s="18">
-        <v>0.09848812314909024</v>
+        <v>0.04643194896820662</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02747356118795669</v>
+        <v>0.04582797212920738</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02680578096301301</v>
+        <v>0.03138312611718257</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03069878469020458</v>
+        <v>0.04056841599912938</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03835295384024685</v>
+        <v>0.03451135772683608</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01263914322878433</v>
+        <v>0.03887564481615886</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0467725534574977</v>
+        <v>0.04648099329366872</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01285848795260781</v>
+        <v>0.03429827625719956</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0265895573417559</v>
+        <v>0.04245119102106724</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01803082192175272</v>
+        <v>0.02589664140727739</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02532410891398964</v>
+        <v>0.0288681738897167</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02744461426597174</v>
+        <v>0.03017816503956089</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01181436003597617</v>
+        <v>0.03787964228376432</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03486042379229944</v>
+        <v>0.03475040407576475</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01247274166590163</v>
+        <v>0.02332217514165191</v>
       </c>
     </row>
   </sheetData>
